--- a/docs/ValueSet-hn-vs-5154109e8985.xlsx
+++ b/docs/ValueSet-hn-vs-5154109e8985.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T17:33:17+08:00</t>
+    <t>2026-09-29T04:34:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
